--- a/data/trans_dic/IP2907_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial</t>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,47; 30,0</t>
+          <t>12,88; 29,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,66; 37,55</t>
+          <t>18,9; 38,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 30,88</t>
+          <t>17,79; 30,47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 23,54</t>
+          <t>11,12; 23,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,63; 26,7</t>
+          <t>12,89; 26,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 22,73</t>
+          <t>13,61; 23,37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 32,41</t>
+          <t>15,07; 32,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,22; 31,65</t>
+          <t>15,03; 31,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,22; 29,18</t>
+          <t>16,1; 28,89</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,54; 36,95</t>
+          <t>17,66; 36,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 38,13</t>
+          <t>12,94; 39,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 33,11</t>
+          <t>18,11; 34,02</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,28; 40,16</t>
+          <t>18,01; 39,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,66; 41,62</t>
+          <t>19,98; 42,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,59; 37,39</t>
+          <t>22,26; 37,46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 20,44</t>
+          <t>5,69; 21,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,16; 21,16</t>
+          <t>7,37; 20,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 18,88</t>
+          <t>7,86; 17,45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,0; 29,93</t>
+          <t>16,87; 31,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,01; 32,72</t>
+          <t>13,9; 32,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,61; 29,24</t>
+          <t>16,98; 28,65</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 15,49</t>
+          <t>6,88; 16,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 16,93</t>
+          <t>7,31; 16,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 14,69</t>
+          <t>8,05; 14,46</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,75; 22,03</t>
+          <t>16,35; 21,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,02; 23,25</t>
+          <t>16,96; 23,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,55; 21,82</t>
+          <t>17,51; 21,83</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>14477</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20588</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35065</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>9197; 21114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14103; 28959</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25968; 44490</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16248</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23045</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39293</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10709; 22234</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15936; 33233</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>29943; 51403</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12537</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14249</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26786</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>8441; 17922</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9524; 19865</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19219; 34484</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17916</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18358</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36274</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11971; 24815</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9558; 29235</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25648; 48194</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9781</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12244</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6160; 13621</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8134; 17222</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16678; 28064</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>4992</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6895</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11887</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2435; 9378</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3966; 11071</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7589; 16850</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>27927</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>32984</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>60910</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>20427; 37543</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>21370; 50632</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>46675; 78735</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>13548</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>17544</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>31092</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>8772; 20697</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>11224; 24982</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>22615; 40620</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>117425</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>145907</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>263332</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>100877; 132963</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>125043; 172695</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>237069; 295702</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2907_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 29,57</t>
+          <t>12,89; 29,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,9; 38,82</t>
+          <t>19,29; 38,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 30,47</t>
+          <t>17,95; 30,98</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 23,09</t>
+          <t>11,46; 24,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,89; 26,87</t>
+          <t>13,0; 27,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 23,37</t>
+          <t>13,62; 23,25</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 32,0</t>
+          <t>14,69; 31,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 31,35</t>
+          <t>14,99; 31,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,1; 28,89</t>
+          <t>16,29; 28,95</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,66; 36,61</t>
+          <t>16,8; 36,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 39,58</t>
+          <t>11,67; 37,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 34,02</t>
+          <t>18,1; 33,99</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,01; 39,83</t>
+          <t>18,04; 39,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,98; 42,29</t>
+          <t>19,9; 41,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,26; 37,46</t>
+          <t>22,75; 38,34</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,69; 21,92</t>
+          <t>5,54; 20,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,37; 20,59</t>
+          <t>7,37; 21,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 17,45</t>
+          <t>8,23; 17,88</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,87; 31,0</t>
+          <t>16,82; 30,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,9; 32,93</t>
+          <t>13,83; 31,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,98; 28,65</t>
+          <t>17,03; 29,25</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,24</t>
+          <t>6,67; 15,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 16,27</t>
+          <t>7,31; 16,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,05; 14,46</t>
+          <t>8,05; 14,84</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,55</t>
+          <t>16,22; 21,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,96; 23,42</t>
+          <t>17,17; 23,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,51; 21,83</t>
+          <t>17,44; 21,46</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9197; 21114</t>
+          <t>9206; 21251</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14103; 28959</t>
+          <t>14389; 28759</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25968; 44490</t>
+          <t>26204; 45228</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10709; 22234</t>
+          <t>11037; 23340</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15936; 33233</t>
+          <t>16074; 33477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29943; 51403</t>
+          <t>29954; 51139</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8441; 17922</t>
+          <t>8224; 17870</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9524; 19865</t>
+          <t>9499; 20239</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19219; 34484</t>
+          <t>19440; 34557</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11971; 24815</t>
+          <t>11385; 24775</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9558; 29235</t>
+          <t>8619; 27801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25648; 48194</t>
+          <t>25642; 48150</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6160; 13621</t>
+          <t>6171; 13611</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8134; 17222</t>
+          <t>8102; 16776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16678; 28064</t>
+          <t>17048; 28722</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2435; 9378</t>
+          <t>2372; 8706</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3966; 11071</t>
+          <t>3964; 11639</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7589; 16850</t>
+          <t>7944; 17271</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20427; 37543</t>
+          <t>20373; 36477</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21370; 50632</t>
+          <t>21271; 48849</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46675; 78735</t>
+          <t>46802; 80397</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8772; 20697</t>
+          <t>8507; 20335</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11224; 24982</t>
+          <t>11221; 25840</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22615; 40620</t>
+          <t>22606; 41710</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>100877; 132963</t>
+          <t>100103; 135554</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>125043; 172695</t>
+          <t>126570; 171111</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>237069; 295702</t>
+          <t>236214; 290681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 29,76</t>
+          <t>20,3; 39,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 38,55</t>
+          <t>15,07; 32,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,95; 30,98</t>
+          <t>19,71; 32,97</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,46; 24,24</t>
+          <t>12,39; 26,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,0; 27,07</t>
+          <t>11,67; 24,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 23,25</t>
+          <t>13,48; 22,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,69; 31,91</t>
+          <t>14,2; 31,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,99; 31,94</t>
+          <t>14,62; 32,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,29; 28,95</t>
+          <t>17,05; 29,3</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,8; 36,55</t>
+          <t>12,96; 38,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 37,64</t>
+          <t>16,14; 35,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,1; 33,99</t>
+          <t>17,8; 32,7</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,04; 39,8</t>
+          <t>20,76; 43,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,9; 41,2</t>
+          <t>17,51; 40,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,75; 38,34</t>
+          <t>21,98; 38,45</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 20,35</t>
+          <t>6,44; 19,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,37; 21,64</t>
+          <t>5,32; 20,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 17,88</t>
+          <t>7,64; 18,05</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,82; 30,12</t>
+          <t>13,6; 29,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,83; 31,77</t>
+          <t>17,93; 30,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,03; 29,25</t>
+          <t>17,22; 27,24</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,67; 15,95</t>
+          <t>6,85; 16,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 16,83</t>
+          <t>6,37; 15,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,05; 14,84</t>
+          <t>7,93; 14,2</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,22; 21,97</t>
+          <t>16,43; 22,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,21</t>
+          <t>16,83; 22,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,44; 21,46</t>
+          <t>17,38; 21,55</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>30376</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9206; 21251</t>
+          <t>12236; 23888</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14389; 28759</t>
+          <t>8278; 17884</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26204; 45228</t>
+          <t>22700; 37980</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>37386</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11037; 23340</t>
+          <t>13924; 30026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16074; 33477</t>
+          <t>10978; 22944</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29954; 51139</t>
+          <t>27838; 47420</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>24708</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8224; 17870</t>
+          <t>7964; 17611</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9499; 20239</t>
+          <t>7972; 17598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19440; 34557</t>
+          <t>18857; 32406</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36274</t>
+          <t>34028</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11385; 24775</t>
+          <t>8862; 26096</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8619; 27801</t>
+          <t>11045; 24058</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25642; 48150</t>
+          <t>24345; 44733</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>22613</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6171; 13611</t>
+          <t>8218; 17112</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8102; 16776</t>
+          <t>6192; 14242</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17048; 28722</t>
+          <t>16472; 28818</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>10598</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2372; 8706</t>
+          <t>3039; 9437</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3964; 11639</t>
+          <t>2278; 8559</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7944; 17271</t>
+          <t>6872; 16247</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27927</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>32984</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60910</t>
+          <t>56009</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20373; 36477</t>
+          <t>18940; 40580</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21271; 48849</t>
+          <t>21332; 36756</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46802; 80397</t>
+          <t>44481; 70346</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>31237</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8507; 20335</t>
+          <t>10704; 25562</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11221; 25840</t>
+          <t>8661; 20819</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22606; 41710</t>
+          <t>23191; 41503</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>117425</t>
+          <t>130749</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246954</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>100103; 135554</t>
+          <t>111678; 150256</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>126570; 171111</t>
+          <t>101842; 133829</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>236214; 290681</t>
+          <t>223274; 276884</t>
         </is>
       </c>
     </row>
